--- a/config/excel/monsters.xlsx
+++ b/config/excel/monsters.xlsx
@@ -423,10 +423,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -637,7 +637,7 @@
         <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>14</v>
       </c>
       <c r="J4" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>15</v>
       </c>
       <c r="J6" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>14</v>
       </c>
       <c r="J8" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>12</v>
       </c>
       <c r="J9" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>18</v>
       </c>
       <c r="J10" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1441,13 +1441,13 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>12</v>
       </c>
       <c r="J11" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1577,6 +1577,386 @@
           <t>#ff6868</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SNAKE_SHOOTER</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>蛇形子弹怪</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>80</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" t="n">
+        <v>24</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>#3a9a72</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>220</v>
+      </c>
+      <c r="O12" t="n">
+        <v>75</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Slime</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Slime</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>snake</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>enemy_snake_bullet</t>
+        </is>
+      </c>
+      <c r="Z12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>#4fd6a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>JUMPER</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>跳跃怪</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>110</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>14</v>
+      </c>
+      <c r="J13" t="n">
+        <v>36</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>#8a8a98</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Werewolf</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Werewolf</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LASER</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>激光怪</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>90</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>13</v>
+      </c>
+      <c r="J14" t="n">
+        <v>22</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>#b89060</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Knight Templar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Knight Templar</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>laser</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MINI_CENTIPEDE</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>迷你千足虫</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>130</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>13</v>
+      </c>
+      <c r="J15" t="n">
+        <v>30</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>#7a5ab0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/excel/monsters.xlsx
+++ b/config/excel/monsters.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1958,6 +1958,99 @@
       </c>
       <c r="AC15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DASHER</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>冲刺怪</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>70</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>#8B0000</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bat</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Bat</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config/excel/monsters.xlsx
+++ b/config/excel/monsters.xlsx
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>

--- a/config/excel/monsters.xlsx
+++ b/config/excel/monsters.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2051,6 +2051,103 @@
       </c>
       <c r="AC16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TELEPORTER</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>瞬移怪</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>80</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>12</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>#5a3a7a</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>320</v>
+      </c>
+      <c r="O17" t="n">
+        <v>140</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Necromancer</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Necromancer</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>enemy_teleport_bolt</t>
+        </is>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
